--- a/Sindhi Muslim/Time Table/Grade 1 - Time Table.xlsx
+++ b/Sindhi Muslim/Time Table/Grade 1 - Time Table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Time Table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\Time Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A873E3AF-3537-49E6-8181-A3DC6503B7D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A594B1-36C7-48FC-908F-56B66522F674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{12A5473C-745C-4A6C-A706-08B2E93F707C}"/>
   </bookViews>
@@ -339,7 +339,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -358,6 +358,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="17">
     <border>
@@ -587,7 +593,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -601,6 +607,27 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -619,25 +646,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -990,189 +999,189 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="7"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="8" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="10"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="17"/>
     </row>
     <row r="7" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="8" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="17" t="s">
+      <c r="G10" s="11" t="s">
         <v>40</v>
       </c>
     </row>
